--- a/staff_list.xlsx
+++ b/staff_list.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\MBA Program\Desktop\Exam_Scheduler\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3985B2CF-D997-473F-B3DB-0D4ADCA812E3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{273D872C-759D-4316-A3BB-A413C82397F3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="12336" xr2:uid="{AD097D11-24AA-4991-B774-33468B1C3668}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AD097D11-24AA-4991-B774-33468B1C3668}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,24 +25,15 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="12" uniqueCount="11">
   <si>
     <t>Name</t>
   </si>
   <si>
-    <t>Role</t>
-  </si>
-  <si>
     <t>Dr. J Ramawickrama</t>
   </si>
   <si>
-    <t>Supervisor</t>
-  </si>
-  <si>
     <t>Sanjeewani</t>
-  </si>
-  <si>
-    <t>Invigilator</t>
   </si>
   <si>
     <t>Prof. H.S. C. Perera</t>
@@ -418,107 +409,70 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AF78F70C-63AA-443B-8292-DD23CBE623D0}">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:A12"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="25.77734375" customWidth="1"/>
-    <col min="2" max="2" width="15.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>2</v>
       </c>
-      <c r="B2" t="s">
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="s">
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
         <v>6</v>
       </c>
-      <c r="B4" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
         <v>7</v>
       </c>
-      <c r="B5" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A6" t="s">
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
         <v>8</v>
       </c>
-      <c r="B6" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A7" t="s">
-        <v>4</v>
-      </c>
-      <c r="B7" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A8" t="s">
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
         <v>9</v>
       </c>
-      <c r="B8" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A9" t="s">
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" t="s">
         <v>10</v>
-      </c>
-      <c r="B9" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>11</v>
-      </c>
-      <c r="B10" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A11" t="s">
-        <v>12</v>
-      </c>
-      <c r="B11" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A12" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" t="s">
-        <v>5</v>
       </c>
     </row>
   </sheetData>
